--- a/data/GPS-Daten_Knotenpunkte.xlsx
+++ b/data/GPS-Daten_Knotenpunkte.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\pwahs\mdzt\route-picker\example\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C1AB828-8D4E-4B5E-8970-709852D746C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1838111F-1E8F-47BF-8CE1-E50A9AC1ECEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-3555" windowWidth="38640" windowHeight="21120" xr2:uid="{23F1768A-3F72-45A9-BD77-FBDC69BB0BBF}"/>
   </bookViews>
   <sheets>
-    <sheet name="ehem. BARnimer Land" sheetId="1" r:id="rId1"/>
+    <sheet name="Barnimer Land" sheetId="1" r:id="rId1"/>
     <sheet name="Nachbarregionen" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -3038,26 +3038,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="bcc43101-2024-4ab1-a533-f1debe28b476" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="a1b2e515-18f6-41bb-93d3-ae289a4d5f75">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x010100D4FB81B1B318F948BEC23BF7923B58F6" ma:contentTypeVersion="19" ma:contentTypeDescription="Ein neues Dokument erstellen." ma:contentTypeScope="" ma:versionID="7e84b9e5ca734c0933fbad4057cd2750">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="bcc43101-2024-4ab1-a533-f1debe28b476" xmlns:ns3="a1b2e515-18f6-41bb-93d3-ae289a4d5f75" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2cbde481a808845b64c50f1e216eef3e" ns2:_="" ns3:_="">
     <xsd:import namespace="bcc43101-2024-4ab1-a533-f1debe28b476"/>
@@ -3312,10 +3292,41 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="bcc43101-2024-4ab1-a533-f1debe28b476" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="a1b2e515-18f6-41bb-93d3-ae289a4d5f75">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AB3C916F-3A2F-4E38-B49A-9D1E5A7BCD42}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AAFFD87C-395B-4A06-811F-660D7A978ECE}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="bcc43101-2024-4ab1-a533-f1debe28b476"/>
+    <ds:schemaRef ds:uri="a1b2e515-18f6-41bb-93d3-ae289a4d5f75"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -3332,20 +3343,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AAFFD87C-395B-4A06-811F-660D7A978ECE}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AB3C916F-3A2F-4E38-B49A-9D1E5A7BCD42}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="bcc43101-2024-4ab1-a533-f1debe28b476"/>
-    <ds:schemaRef ds:uri="a1b2e515-18f6-41bb-93d3-ae289a4d5f75"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>